--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846053</v>
+        <v>119846058</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,29 +1437,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1469,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475162</v>
+        <v>475168</v>
       </c>
       <c r="R9" t="n">
-        <v>6824667</v>
+        <v>6824676</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1505,11 +1509,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846058</v>
+        <v>119846053</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,33 +1551,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475168</v>
+        <v>475162</v>
       </c>
       <c r="R10" t="n">
-        <v>6824676</v>
+        <v>6824667</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1624,6 +1619,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846058</v>
+        <v>119846053</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,33 +1437,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1473,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475168</v>
+        <v>475162</v>
       </c>
       <c r="R9" t="n">
-        <v>6824676</v>
+        <v>6824667</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1509,6 +1505,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846053</v>
+        <v>119846058</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,29 +1552,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1583,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475162</v>
+        <v>475168</v>
       </c>
       <c r="R10" t="n">
-        <v>6824667</v>
+        <v>6824676</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1619,11 +1624,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119845968</v>
+        <v>119846053</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475107</v>
+        <v>475162</v>
       </c>
       <c r="R2" t="n">
-        <v>6824742</v>
+        <v>6824667</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -756,13 +761,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119845955</v>
+        <v>119845959</v>
       </c>
       <c r="B3" t="n">
         <v>78560</v>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475112</v>
+        <v>475110</v>
       </c>
       <c r="R3" t="n">
-        <v>6824743</v>
+        <v>6824738</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845976</v>
+        <v>119846030</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +912,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475116</v>
+        <v>475161</v>
       </c>
       <c r="R4" t="n">
-        <v>6824750</v>
+        <v>6824668</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +983,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846028</v>
+        <v>119846029</v>
       </c>
       <c r="B5" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475131</v>
+        <v>475163</v>
       </c>
       <c r="R5" t="n">
-        <v>6824706</v>
+        <v>6824677</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846030</v>
+        <v>119845976</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,26 +1124,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475161</v>
+        <v>475116</v>
       </c>
       <c r="R6" t="n">
-        <v>6824668</v>
+        <v>6824750</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1209,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846026</v>
+        <v>119845988</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475133</v>
+        <v>475122</v>
       </c>
       <c r="R7" t="n">
-        <v>6824711</v>
+        <v>6824759</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846013</v>
+        <v>119846028</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1340,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475121</v>
+        <v>475131</v>
       </c>
       <c r="R8" t="n">
-        <v>6824767</v>
+        <v>6824706</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846053</v>
+        <v>119846026</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,31 +1446,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1469,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475162</v>
+        <v>475133</v>
       </c>
       <c r="R9" t="n">
-        <v>6824667</v>
+        <v>6824711</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,17 +1511,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119845959</v>
+        <v>119845968</v>
       </c>
       <c r="B11" t="n">
         <v>78560</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475110</v>
+        <v>475107</v>
       </c>
       <c r="R11" t="n">
-        <v>6824738</v>
+        <v>6824742</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846021</v>
+        <v>119845955</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>78560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475136</v>
+        <v>475112</v>
       </c>
       <c r="R12" t="n">
-        <v>6824732</v>
+        <v>6824743</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1968,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119845988</v>
+        <v>119846013</v>
       </c>
       <c r="B14" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475122</v>
+        <v>475121</v>
       </c>
       <c r="R14" t="n">
-        <v>6824759</v>
+        <v>6824767</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846029</v>
+        <v>119846021</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475163</v>
+        <v>475136</v>
       </c>
       <c r="R15" t="n">
-        <v>6824677</v>
+        <v>6824732</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846053</v>
+        <v>119846058</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475162</v>
+        <v>475168</v>
       </c>
       <c r="R2" t="n">
-        <v>6824667</v>
+        <v>6824676</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119845959</v>
+        <v>119846021</v>
       </c>
       <c r="B3" t="n">
-        <v>78560</v>
+        <v>79607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475110</v>
+        <v>475136</v>
       </c>
       <c r="R3" t="n">
-        <v>6824738</v>
+        <v>6824732</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119846030</v>
+        <v>119845988</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475161</v>
+        <v>475122</v>
       </c>
       <c r="R4" t="n">
-        <v>6824668</v>
+        <v>6824759</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846029</v>
+        <v>119845976</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,26 +1017,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475163</v>
+        <v>475116</v>
       </c>
       <c r="R5" t="n">
-        <v>6824677</v>
+        <v>6824750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1093,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119845976</v>
+        <v>119845959</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78560</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,31 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475116</v>
+        <v>475110</v>
       </c>
       <c r="R6" t="n">
-        <v>6824750</v>
+        <v>6824738</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,6 +1198,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1218,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119845988</v>
+        <v>119846030</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475122</v>
+        <v>475161</v>
       </c>
       <c r="R7" t="n">
-        <v>6824759</v>
+        <v>6824668</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1430,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846026</v>
+        <v>119846029</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1473,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475133</v>
+        <v>475163</v>
       </c>
       <c r="R9" t="n">
-        <v>6824711</v>
+        <v>6824677</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1536,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846058</v>
+        <v>119845968</v>
       </c>
       <c r="B10" t="n">
-        <v>57463</v>
+        <v>78560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,35 +1551,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475168</v>
+        <v>475107</v>
       </c>
       <c r="R10" t="n">
-        <v>6824676</v>
+        <v>6824742</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1632,6 +1622,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1641,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119845968</v>
+        <v>119845955</v>
       </c>
       <c r="B11" t="n">
         <v>78560</v>
@@ -1693,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475107</v>
+        <v>475112</v>
       </c>
       <c r="R11" t="n">
-        <v>6824742</v>
+        <v>6824743</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119845955</v>
+        <v>119846053</v>
       </c>
       <c r="B12" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,26 +1763,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1799,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475112</v>
+        <v>475162</v>
       </c>
       <c r="R12" t="n">
-        <v>6824743</v>
+        <v>6824667</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1837,13 +1833,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119845963</v>
+        <v>119846026</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475107</v>
+        <v>475133</v>
       </c>
       <c r="R13" t="n">
-        <v>6824740</v>
+        <v>6824711</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846021</v>
+        <v>119845963</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475136</v>
+        <v>475107</v>
       </c>
       <c r="R15" t="n">
-        <v>6824732</v>
+        <v>6824740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846058</v>
+        <v>119845968</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>78560</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475168</v>
+        <v>475107</v>
       </c>
       <c r="R2" t="n">
-        <v>6824676</v>
+        <v>6824742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846021</v>
+        <v>119846026</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475136</v>
+        <v>475133</v>
       </c>
       <c r="R3" t="n">
-        <v>6824732</v>
+        <v>6824711</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845988</v>
+        <v>119845955</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>78560</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475122</v>
+        <v>475112</v>
       </c>
       <c r="R4" t="n">
-        <v>6824759</v>
+        <v>6824743</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119845976</v>
+        <v>119846029</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,31 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475116</v>
+        <v>475163</v>
       </c>
       <c r="R5" t="n">
-        <v>6824750</v>
+        <v>6824677</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1093,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1111,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119845959</v>
+        <v>119846058</v>
       </c>
       <c r="B6" t="n">
-        <v>78560</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,26 +1115,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475110</v>
+        <v>475168</v>
       </c>
       <c r="R6" t="n">
-        <v>6824738</v>
+        <v>6824676</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1217,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846030</v>
+        <v>119845959</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475161</v>
+        <v>475110</v>
       </c>
       <c r="R7" t="n">
-        <v>6824668</v>
+        <v>6824738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1429,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846029</v>
+        <v>119845976</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,26 +1441,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1472,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475163</v>
+        <v>475116</v>
       </c>
       <c r="R9" t="n">
-        <v>6824677</v>
+        <v>6824750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1516,7 +1517,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119845968</v>
+        <v>119846053</v>
       </c>
       <c r="B10" t="n">
-        <v>78560</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,26 +1551,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1578,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475107</v>
+        <v>475162</v>
       </c>
       <c r="R10" t="n">
-        <v>6824742</v>
+        <v>6824667</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1616,13 +1621,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1641,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119845955</v>
+        <v>119846021</v>
       </c>
       <c r="B11" t="n">
-        <v>78560</v>
+        <v>79607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,21 +1666,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475112</v>
+        <v>475136</v>
       </c>
       <c r="R11" t="n">
-        <v>6824743</v>
+        <v>6824732</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1747,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846053</v>
+        <v>119846013</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1763,31 +1772,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1795,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475162</v>
+        <v>475121</v>
       </c>
       <c r="R12" t="n">
-        <v>6824667</v>
+        <v>6824767</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1833,17 +1837,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846026</v>
+        <v>119846030</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475133</v>
+        <v>475161</v>
       </c>
       <c r="R13" t="n">
-        <v>6824711</v>
+        <v>6824668</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846013</v>
+        <v>119845963</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475121</v>
+        <v>475107</v>
       </c>
       <c r="R14" t="n">
-        <v>6824767</v>
+        <v>6824740</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119845963</v>
+        <v>119845988</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79144</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475107</v>
+        <v>475122</v>
       </c>
       <c r="R15" t="n">
-        <v>6824740</v>
+        <v>6824759</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119845968</v>
+        <v>119846029</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475107</v>
+        <v>475163</v>
       </c>
       <c r="R2" t="n">
-        <v>6824742</v>
+        <v>6824677</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846026</v>
+        <v>119846028</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475133</v>
+        <v>475131</v>
       </c>
       <c r="R3" t="n">
-        <v>6824711</v>
+        <v>6824706</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845955</v>
+        <v>119845988</v>
       </c>
       <c r="B4" t="n">
-        <v>78560</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475112</v>
+        <v>475122</v>
       </c>
       <c r="R4" t="n">
-        <v>6824743</v>
+        <v>6824759</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846029</v>
+        <v>119846013</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475163</v>
+        <v>475121</v>
       </c>
       <c r="R5" t="n">
-        <v>6824677</v>
+        <v>6824767</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846058</v>
+        <v>119845963</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,35 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475168</v>
+        <v>475107</v>
       </c>
       <c r="R6" t="n">
-        <v>6824676</v>
+        <v>6824740</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119845959</v>
+        <v>119846026</v>
       </c>
       <c r="B7" t="n">
-        <v>78560</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1256,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475110</v>
+        <v>475133</v>
       </c>
       <c r="R7" t="n">
-        <v>6824738</v>
+        <v>6824711</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846028</v>
+        <v>119845959</v>
       </c>
       <c r="B8" t="n">
-        <v>78560</v>
+        <v>78576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475131</v>
+        <v>475110</v>
       </c>
       <c r="R8" t="n">
-        <v>6824706</v>
+        <v>6824738</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1425,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119845976</v>
+        <v>119846021</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,31 +1433,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1473,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475116</v>
+        <v>475136</v>
       </c>
       <c r="R9" t="n">
-        <v>6824750</v>
+        <v>6824732</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1517,6 +1504,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1538,7 +1526,7 @@
         <v>119846053</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846021</v>
+        <v>119846030</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475136</v>
+        <v>475161</v>
       </c>
       <c r="R11" t="n">
-        <v>6824732</v>
+        <v>6824668</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846013</v>
+        <v>119846058</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57473</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,26 +1760,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1799,10 +1796,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475121</v>
+        <v>475168</v>
       </c>
       <c r="R12" t="n">
-        <v>6824767</v>
+        <v>6824676</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,7 +1840,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1862,10 +1858,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846030</v>
+        <v>119845976</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,26 +1874,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1905,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475161</v>
+        <v>475116</v>
       </c>
       <c r="R13" t="n">
-        <v>6824668</v>
+        <v>6824750</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,7 +1950,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1968,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119845963</v>
+        <v>119845968</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
         <v>475107</v>
       </c>
       <c r="R14" t="n">
-        <v>6824740</v>
+        <v>6824742</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119845988</v>
+        <v>119845955</v>
       </c>
       <c r="B15" t="n">
-        <v>79144</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475122</v>
+        <v>475112</v>
       </c>
       <c r="R15" t="n">
-        <v>6824759</v>
+        <v>6824743</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846029</v>
+        <v>119845968</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475163</v>
+        <v>475107</v>
       </c>
       <c r="R2" t="n">
-        <v>6824677</v>
+        <v>6824742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845988</v>
+        <v>119845963</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475122</v>
+        <v>475107</v>
       </c>
       <c r="R4" t="n">
-        <v>6824759</v>
+        <v>6824740</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119846013</v>
+        <v>119845976</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1009,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475121</v>
+        <v>475116</v>
       </c>
       <c r="R5" t="n">
-        <v>6824767</v>
+        <v>6824750</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,7 +1085,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119845963</v>
+        <v>119846030</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1142,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475107</v>
+        <v>475161</v>
       </c>
       <c r="R6" t="n">
-        <v>6824740</v>
+        <v>6824668</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119846026</v>
+        <v>119845959</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475133</v>
+        <v>475110</v>
       </c>
       <c r="R7" t="n">
-        <v>6824711</v>
+        <v>6824738</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1311,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119845959</v>
+        <v>119846021</v>
       </c>
       <c r="B8" t="n">
-        <v>78576</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475110</v>
+        <v>475136</v>
       </c>
       <c r="R8" t="n">
-        <v>6824738</v>
+        <v>6824732</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119846021</v>
+        <v>119845955</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475136</v>
+        <v>475112</v>
       </c>
       <c r="R9" t="n">
-        <v>6824732</v>
+        <v>6824743</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846053</v>
+        <v>119846013</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,31 +1543,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1571,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475162</v>
+        <v>475121</v>
       </c>
       <c r="R10" t="n">
-        <v>6824667</v>
+        <v>6824767</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1609,17 +1608,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1638,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846030</v>
+        <v>119846053</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,26 +1649,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475161</v>
+        <v>475162</v>
       </c>
       <c r="R11" t="n">
-        <v>6824668</v>
+        <v>6824667</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1719,13 +1719,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1744,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846058</v>
+        <v>119846029</v>
       </c>
       <c r="B12" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,35 +1764,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475168</v>
+        <v>475163</v>
       </c>
       <c r="R12" t="n">
-        <v>6824676</v>
+        <v>6824677</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,6 +1835,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1858,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119845976</v>
+        <v>119845988</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,31 +1870,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1906,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475116</v>
+        <v>475122</v>
       </c>
       <c r="R13" t="n">
-        <v>6824750</v>
+        <v>6824759</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1950,6 +1941,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119845968</v>
+        <v>119846058</v>
       </c>
       <c r="B14" t="n">
-        <v>78576</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,26 +1976,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2011,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475107</v>
+        <v>475168</v>
       </c>
       <c r="R14" t="n">
-        <v>6824742</v>
+        <v>6824676</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2055,7 +2056,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119845955</v>
+        <v>119846026</v>
       </c>
       <c r="B15" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475112</v>
+        <v>475133</v>
       </c>
       <c r="R15" t="n">
-        <v>6824743</v>
+        <v>6824711</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119845968</v>
+        <v>119846029</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475107</v>
+        <v>475163</v>
       </c>
       <c r="R2" t="n">
-        <v>6824742</v>
+        <v>6824677</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119846028</v>
+        <v>119845963</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475131</v>
+        <v>475107</v>
       </c>
       <c r="R3" t="n">
-        <v>6824706</v>
+        <v>6824740</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845963</v>
+        <v>119845976</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475107</v>
+        <v>475116</v>
       </c>
       <c r="R4" t="n">
-        <v>6824740</v>
+        <v>6824750</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +979,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119845976</v>
+        <v>119846026</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,31 +1013,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475116</v>
+        <v>475133</v>
       </c>
       <c r="R5" t="n">
-        <v>6824750</v>
+        <v>6824711</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1084,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119846030</v>
+        <v>119845959</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475161</v>
+        <v>475110</v>
       </c>
       <c r="R6" t="n">
-        <v>6824668</v>
+        <v>6824738</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119845959</v>
+        <v>119845968</v>
       </c>
       <c r="B7" t="n">
         <v>78576</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475110</v>
+        <v>475107</v>
       </c>
       <c r="R7" t="n">
-        <v>6824738</v>
+        <v>6824742</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119845955</v>
+        <v>119845988</v>
       </c>
       <c r="B9" t="n">
-        <v>78576</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475112</v>
+        <v>475122</v>
       </c>
       <c r="R9" t="n">
-        <v>6824743</v>
+        <v>6824759</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119846013</v>
+        <v>119846030</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475121</v>
+        <v>475161</v>
       </c>
       <c r="R10" t="n">
-        <v>6824767</v>
+        <v>6824668</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846053</v>
+        <v>119846013</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,31 +1649,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475162</v>
+        <v>475121</v>
       </c>
       <c r="R11" t="n">
-        <v>6824667</v>
+        <v>6824767</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1719,17 +1714,13 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1748,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119846029</v>
+        <v>119845955</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1782,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475163</v>
+        <v>475112</v>
       </c>
       <c r="R12" t="n">
-        <v>6824677</v>
+        <v>6824743</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1854,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119845988</v>
+        <v>119846058</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,26 +1861,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475122</v>
+        <v>475168</v>
       </c>
       <c r="R13" t="n">
-        <v>6824759</v>
+        <v>6824676</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1941,7 +1941,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846058</v>
+        <v>119846028</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,35 +1975,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2012,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475168</v>
+        <v>475131</v>
       </c>
       <c r="R14" t="n">
-        <v>6824676</v>
+        <v>6824706</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2056,6 +2046,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2074,10 +2065,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846026</v>
+        <v>119846053</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,26 +2081,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2117,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475133</v>
+        <v>475162</v>
       </c>
       <c r="R15" t="n">
-        <v>6824711</v>
+        <v>6824667</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2155,13 +2151,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119846029</v>
+        <v>119845968</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475163</v>
+        <v>475107</v>
       </c>
       <c r="R2" t="n">
-        <v>6824677</v>
+        <v>6824742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119845963</v>
+        <v>119846013</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475107</v>
+        <v>475121</v>
       </c>
       <c r="R3" t="n">
-        <v>6824740</v>
+        <v>6824767</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119845976</v>
+        <v>119845988</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,31 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475116</v>
+        <v>475122</v>
       </c>
       <c r="R4" t="n">
-        <v>6824750</v>
+        <v>6824759</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119845959</v>
+        <v>119846021</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475110</v>
+        <v>475136</v>
       </c>
       <c r="R6" t="n">
-        <v>6824738</v>
+        <v>6824732</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119845968</v>
+        <v>119846028</v>
       </c>
       <c r="B7" t="n">
         <v>78576</v>
@@ -1252,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475107</v>
+        <v>475131</v>
       </c>
       <c r="R7" t="n">
-        <v>6824742</v>
+        <v>6824706</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119846021</v>
+        <v>119846029</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1358,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475136</v>
+        <v>475163</v>
       </c>
       <c r="R8" t="n">
-        <v>6824732</v>
+        <v>6824677</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119845988</v>
+        <v>119845976</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,26 +1433,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1464,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475122</v>
+        <v>475116</v>
       </c>
       <c r="R9" t="n">
-        <v>6824759</v>
+        <v>6824750</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,7 +1509,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119846013</v>
+        <v>119845963</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475121</v>
+        <v>475107</v>
       </c>
       <c r="R11" t="n">
-        <v>6824767</v>
+        <v>6824740</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119846058</v>
+        <v>119845959</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>78576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,35 +1861,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1897,10 +1888,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475168</v>
+        <v>475110</v>
       </c>
       <c r="R13" t="n">
-        <v>6824676</v>
+        <v>6824738</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1941,6 +1932,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1959,10 +1951,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119846028</v>
+        <v>119846053</v>
       </c>
       <c r="B14" t="n">
-        <v>78576</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,26 +1967,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2002,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475131</v>
+        <v>475162</v>
       </c>
       <c r="R14" t="n">
-        <v>6824706</v>
+        <v>6824667</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2040,13 +2037,17 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringat träd, gammal gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2065,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119846053</v>
+        <v>119846058</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,29 +2082,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2113,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475162</v>
+        <v>475168</v>
       </c>
       <c r="R15" t="n">
-        <v>6824667</v>
+        <v>6824676</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,11 +2154,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringat träd, gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>119845976</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>119846053</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 35557-2023 artfynd.xlsx
+++ b/artfynd/A 35557-2023 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>119845976</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>119846053</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
